--- a/projects/04-08-darktrace/models/Darktrace_04_08.xlsx
+++ b/projects/04-08-darktrace/models/Darktrace_04_08.xlsx
@@ -33,12 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="583">
   <si>
     <t xml:space="preserve">Darktrace plc / Thoma Bravo take-private (2024)</t>
   </si>
   <si>
-    <t xml:space="preserve">Project 04: sell-side fairness view. Project 08: LBO and IC case. Built from the Rule 2.7 announcement, scheme document and company releases.</t>
+    <t xml:space="preserve">Project 04: sell-side fairness view. Project 08: LBO and IC case. Retrospective analysis: April market inputs, July FY24 update; not an April information set.</t>
   </si>
   <si>
     <t xml:space="preserve">Tobenna Agubuche | github.com/Tobenna30/finance-models | Not investment advice</t>
@@ -95,9 +95,18 @@
     <t xml:space="preserve">Debt / LTM EBITDA at close</t>
   </si>
   <si>
+    <t xml:space="preserve">Base liquidity low point ($m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base shortfall to operating cash minimum ($m)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Downside liquidity low point ($m)</t>
   </si>
   <si>
+    <t xml:space="preserve">Downside shortfall to operating cash minimum ($m)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bridge check (should be 0)</t>
   </si>
   <si>
@@ -218,7 +227,7 @@
     <t xml:space="preserve">% ISC</t>
   </si>
   <si>
-    <t xml:space="preserve">SCH: Publication of Scheme Document, 23 May 2024</t>
+    <t xml:space="preserve">SCH: Scheme document, 23 May 2024, pp. 15, 19, 28 and 87 (offer, undertakings, interim financing)</t>
   </si>
   <si>
     <t xml:space="preserve">Court Meeting: Scheme Shares voted in favour</t>
@@ -1163,7 +1172,7 @@
     <t xml:space="preserve">Offer</t>
   </si>
   <si>
-    <t xml:space="preserve">52-week trading (placing to 12m high)</t>
+    <t xml:space="preserve">March placing to 12-month high</t>
   </si>
   <si>
     <t xml:space="preserve">DCF (WACC +/-1%, g +/-0.5%)</t>
@@ -1475,10 +1484,10 @@
     <t xml:space="preserve">SCH</t>
   </si>
   <si>
-    <t xml:space="preserve">Publication of Scheme Document, 23 May 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ir.darktrace.com/regulatory-news/2024/5/23/1823676</t>
+    <t xml:space="preserve">Scheme document, 23 May 2024, pp. 15, 19, 28 and 87 (offer, undertakings, interim financing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.fca.org.uk/artefacts/NSM/Portal/NI-000097497/NI-000097497.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">VOTE</t>
@@ -2265,16 +2274,6 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2287,7 +2286,7 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>52-week trading (placing to 12m high)</c:v>
+                  <c:v>March placing to 12-month high</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>DCF (WACC +/-1%, g +/-0.5%)</c:v>
@@ -2383,16 +2382,6 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2405,7 +2394,7 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>52-week trading (placing to 12m high)</c:v>
+                  <c:v>March placing to 12-month high</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>DCF (WACC +/-1%, g +/-0.5%)</c:v>
@@ -2461,11 +2450,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="36977016"/>
-        <c:axId val="53036962"/>
+        <c:axId val="3484743"/>
+        <c:axId val="43544524"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="36977016"/>
+        <c:axId val="3484743"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2498,7 +2487,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53036962"/>
+        <c:crossAx val="43544524"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2506,7 +2495,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53036962"/>
+        <c:axId val="43544524"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2549,14 +2538,11 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36977016"/>
+        <c:crossAx val="3484743"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2566,9 +2552,6 @@
     <c:dispBlanksAs val="gap"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
@@ -2582,6 +2565,11 @@
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
 </cs:colorStyle>
 </file>
 
@@ -3010,10 +2998,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
@@ -3190,8 +3178,8 @@
         <v>20</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">Downside!$B$52</f>
-        <v>19.180054982674</v>
+        <f aca="false">LBO!$B$56</f>
+        <v>77.8348235902022</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3199,6 +3187,33 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="n">
+        <f aca="false">MAX(0,Inputs!$C$79-LBO!$B$56)</f>
+        <v>22.1651764097979</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <f aca="false">Downside!$B$52</f>
+        <v>19.180054982674</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <f aca="false">MAX(0,Inputs!$C$79-Downside!$B$52)</f>
+        <v>80.819945017326</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="6" t="n">
         <f aca="false">LBO!$B$66</f>
         <v>0</v>
       </c>
@@ -3228,17 +3243,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J3" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K3" s="5" t="n">
         <f aca="false">Inputs!$C$66+Inputs!$C$71</f>
@@ -3247,15 +3262,15 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J4" s="25" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">LBO!$K$3</f>
@@ -3267,7 +3282,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">B5*Inputs!$C$66/(Inputs!$C$66+Inputs!$C$71)</f>
@@ -3279,7 +3294,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B7" s="33" t="n">
         <f aca="false">B5-B6</f>
@@ -3291,7 +3306,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">Inputs!$C$7*Inputs!$C$99</f>
@@ -3303,7 +3318,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">B8-Inputs!$C$100</f>
@@ -3315,7 +3330,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">B6*(1-Inputs!$C$68)+B7*(1-Inputs!$C$73)</f>
@@ -3324,7 +3339,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">B5*Inputs!$C$76</f>
@@ -3333,7 +3348,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B12" s="6" t="n">
         <f aca="false">B9*Inputs!$C$77</f>
@@ -3342,7 +3357,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B13" s="37" t="n">
         <f aca="false">B8+B10+B11+B12</f>
@@ -3351,7 +3366,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B14" s="6" t="n">
         <f aca="false">Inputs!$C$78-Inputs!$C$79</f>
@@ -3360,7 +3375,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B15" s="37" t="n">
         <f aca="false">B13-B5-B14</f>
@@ -3369,7 +3384,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B16" s="24" t="n">
         <f aca="false">B15/B13</f>
@@ -3378,7 +3393,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B17" s="4" t="n">
         <f aca="false">B5/Inputs!$C$12</f>
@@ -3387,7 +3402,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B18" s="4" t="n">
         <f aca="false">B5/Inputs!$C$33</f>
@@ -3396,30 +3411,30 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">History!D5</f>
@@ -3448,7 +3463,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C22" s="3" t="n">
         <f aca="false">Inputs!$F$88</f>
@@ -3473,7 +3488,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C23" s="27" t="n">
         <f aca="false">C21*C24</f>
@@ -3498,7 +3513,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C24" s="3" t="n">
         <f aca="false">Inputs!$F$89</f>
@@ -3523,7 +3538,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C25" s="6" t="n">
         <f aca="false">C21*Inputs!$C$101</f>
@@ -3548,7 +3563,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C26" s="6" t="n">
         <f aca="false">(C21-B21)*Inputs!$C$46</f>
@@ -3573,7 +3588,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C27" s="6" t="n">
         <f aca="false">C21*Inputs!$C$102</f>
@@ -3598,7 +3613,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C28" s="38" t="n">
         <f aca="false">Inputs!$C$84</f>
@@ -3623,7 +3638,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C29" s="22" t="n">
         <f aca="false">Inputs!$F$75</f>
@@ -3648,7 +3663,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C30" s="27" t="n">
         <f aca="false">$B$6</f>
@@ -3673,7 +3688,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C31" s="6" t="n">
         <f aca="false">C30*(C29+Inputs!$C$67)*C28</f>
@@ -3698,7 +3713,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C32" s="6" t="n">
         <f aca="false">C42*(C29+Inputs!$C$72)*C28</f>
@@ -3723,7 +3738,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C33" s="27" t="n">
         <f aca="false">C31+C32</f>
@@ -3748,7 +3763,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C34" s="6" t="n">
         <f aca="false">MIN(C33,Inputs!$C$45*C23*C28)</f>
@@ -3773,7 +3788,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C35" s="6" t="n">
         <f aca="false">MAX(0,(C23-C27)*C28-C34)*Inputs!$C$44</f>
@@ -3798,7 +3813,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C36" s="28" t="n">
         <f aca="false">(C23-C25+C26-Inputs!$C$81)*C28-C33-C35</f>
@@ -3823,7 +3838,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C37" s="6" t="n">
         <f aca="false">MIN(C30,$B$6*Inputs!$C$70*C28)</f>
@@ -3848,7 +3863,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C38" s="6" t="n">
         <f aca="false">Inputs!$C$79</f>
@@ -3873,7 +3888,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C39" s="27" t="n">
         <f aca="false">C38+C36-C37</f>
@@ -3898,7 +3913,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C40" s="6" t="n">
         <f aca="false">MIN(MAX(0,C39-Inputs!$C$79)*Inputs!$C$80,C30-C37)</f>
@@ -3923,7 +3938,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C41" s="27" t="n">
         <f aca="false">C30-C37-C40</f>
@@ -3948,7 +3963,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C42" s="27" t="n">
         <f aca="false">$B$7</f>
@@ -3973,7 +3988,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C43" s="27" t="n">
         <f aca="false">C39-C40</f>
@@ -3998,7 +4013,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C44" s="39" t="n">
         <f aca="false">C41+C42-C43</f>
@@ -4023,7 +4038,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C45" s="32" t="n">
         <f aca="false">(C41+C42)/C23</f>
@@ -4048,7 +4063,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C46" s="32" t="n">
         <f aca="false">C23*C28/C33</f>
@@ -4073,28 +4088,28 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4279,7 +4294,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B56" s="27" t="n">
         <f aca="false">MIN(C43:G43)</f>
@@ -4288,12 +4303,12 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B59" s="33" t="n">
         <f aca="false">$B$15</f>
@@ -4302,7 +4317,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B60" s="5" t="n">
         <f aca="false">(G23-Inputs!$C$12)*($B$9/Inputs!$C$12)</f>
@@ -4311,7 +4326,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B61" s="5" t="n">
         <f aca="false">($B$49-$B$9/Inputs!$C$12)*G23</f>
@@ -4320,7 +4335,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B62" s="5" t="n">
         <f aca="false">($B$5-Inputs!$C$79+Inputs!$C$26)-(G44+Inputs!$C$83)</f>
@@ -4329,7 +4344,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B63" s="33" t="n">
         <f aca="false">-($B$10+$B$11+$B$12)</f>
@@ -4338,7 +4353,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B64" s="5" t="n">
         <f aca="false">-$E$49*Inputs!$C$82</f>
@@ -4347,7 +4362,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B65" s="37" t="n">
         <f aca="false">SUM(B59:B64)</f>
@@ -4356,7 +4371,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B66" s="33" t="n">
         <f aca="false">B65-$F$49</f>
@@ -4388,22 +4403,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">LBO!$K$3</f>
@@ -4412,7 +4427,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">B5*Inputs!$C$66/(Inputs!$C$66+Inputs!$C$71)</f>
@@ -4421,7 +4436,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B7" s="33" t="n">
         <f aca="false">B5-B6</f>
@@ -4430,7 +4445,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">Inputs!$C$7*Inputs!$C$99</f>
@@ -4439,7 +4454,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">B8-Inputs!$C$100</f>
@@ -4448,7 +4463,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">B6*(1-Inputs!$C$68)+B7*(1-Inputs!$C$73)</f>
@@ -4457,7 +4472,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">B5*Inputs!$C$76</f>
@@ -4466,7 +4481,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B12" s="6" t="n">
         <f aca="false">B9*Inputs!$C$77</f>
@@ -4475,7 +4490,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B13" s="37" t="n">
         <f aca="false">B8+B10+B11+B12</f>
@@ -4484,7 +4499,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B14" s="6" t="n">
         <f aca="false">Inputs!$C$78-Inputs!$C$79</f>
@@ -4493,7 +4508,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B15" s="37" t="n">
         <f aca="false">B13-B5-B14</f>
@@ -4502,7 +4517,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B16" s="24" t="n">
         <f aca="false">B15/B13</f>
@@ -4511,7 +4526,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B17" s="4" t="n">
         <f aca="false">B5/Inputs!$C$12</f>
@@ -4520,7 +4535,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B18" s="4" t="n">
         <f aca="false">B5/Inputs!$C$33</f>
@@ -4529,30 +4544,30 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">History!D5</f>
@@ -4581,7 +4596,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C22" s="3" t="n">
         <f aca="false">Inputs!$F$93</f>
@@ -4606,7 +4621,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C23" s="27" t="n">
         <f aca="false">C21*C24</f>
@@ -4631,7 +4646,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C24" s="3" t="n">
         <f aca="false">Inputs!$F$94</f>
@@ -4656,7 +4671,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C25" s="6" t="n">
         <f aca="false">C21*Inputs!$C$101</f>
@@ -4681,7 +4696,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C26" s="6" t="n">
         <f aca="false">(C21-B21)*Inputs!$C$46</f>
@@ -4706,7 +4721,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C27" s="6" t="n">
         <f aca="false">C21*Inputs!$C$102</f>
@@ -4731,7 +4746,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C28" s="38" t="n">
         <f aca="false">Inputs!$C$84</f>
@@ -4756,7 +4771,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C29" s="22" t="n">
         <f aca="false">Inputs!$F$75</f>
@@ -4781,7 +4796,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C30" s="27" t="n">
         <f aca="false">$B$6</f>
@@ -4806,7 +4821,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C31" s="6" t="n">
         <f aca="false">C30*(C29+Inputs!$C$67)*C28</f>
@@ -4831,7 +4846,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C32" s="6" t="n">
         <f aca="false">C42*(C29+Inputs!$C$72)*C28</f>
@@ -4856,7 +4871,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C33" s="27" t="n">
         <f aca="false">C31+C32</f>
@@ -4881,7 +4896,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C34" s="6" t="n">
         <f aca="false">MIN(C33,Inputs!$C$45*C23*C28)</f>
@@ -4906,7 +4921,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C35" s="6" t="n">
         <f aca="false">MAX(0,(C23-C27)*C28-C34)*Inputs!$C$44</f>
@@ -4931,7 +4946,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C36" s="28" t="n">
         <f aca="false">(C23-C25+C26-Inputs!$C$81)*C28-C33-C35</f>
@@ -4956,7 +4971,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C37" s="6" t="n">
         <f aca="false">MIN(C30,$B$6*Inputs!$C$70*C28)</f>
@@ -4981,7 +4996,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C38" s="6" t="n">
         <f aca="false">Inputs!$C$79</f>
@@ -5006,7 +5021,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C39" s="27" t="n">
         <f aca="false">C38+C36-C37</f>
@@ -5031,7 +5046,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C40" s="6" t="n">
         <f aca="false">MIN(MAX(0,C39-Inputs!$C$79)*Inputs!$C$80,C30-C37)</f>
@@ -5056,7 +5071,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C41" s="27" t="n">
         <f aca="false">C30-C37-C40</f>
@@ -5081,7 +5096,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C42" s="27" t="n">
         <f aca="false">$B$7</f>
@@ -5106,7 +5121,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C43" s="27" t="n">
         <f aca="false">C39-C40</f>
@@ -5131,7 +5146,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C44" s="39" t="n">
         <f aca="false">C41+C42-C43</f>
@@ -5156,7 +5171,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C45" s="32" t="n">
         <f aca="false">(C41+C42)/C23</f>
@@ -5181,7 +5196,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C46" s="32" t="n">
         <f aca="false">C23*C28/C33</f>
@@ -5206,28 +5221,28 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5292,7 +5307,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B52" s="27" t="n">
         <f aca="false">MIN(C43:G43)</f>
@@ -5323,17 +5338,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>1500</v>
@@ -5353,7 +5368,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B4" s="4" t="n">
         <f aca="false">B3/Inputs!$C$12</f>
@@ -5378,7 +5393,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5533,12 +5548,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="36" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B16" s="5" t="n">
         <f aca="false">'LBO grid'!$B$3</f>
@@ -5547,7 +5562,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B17" s="5" t="n">
         <f aca="false">B16*Inputs!$C$66/(Inputs!$C$66+Inputs!$C$71)</f>
@@ -5556,7 +5571,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B18" s="33" t="n">
         <f aca="false">B16-B17</f>
@@ -5565,7 +5580,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B19" s="5" t="n">
         <f aca="false">Inputs!$C$7*Inputs!$C$99</f>
@@ -5574,7 +5589,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B20" s="5" t="n">
         <f aca="false">B19-Inputs!$C$100</f>
@@ -5583,7 +5598,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B17*(1-Inputs!$C$68)+B18*(1-Inputs!$C$73)</f>
@@ -5592,7 +5607,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">B16*Inputs!$C$76</f>
@@ -5601,7 +5616,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B23" s="6" t="n">
         <f aca="false">B20*Inputs!$C$77</f>
@@ -5610,7 +5625,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B24" s="37" t="n">
         <f aca="false">B19+B21+B22+B23</f>
@@ -5619,7 +5634,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B25" s="6" t="n">
         <f aca="false">Inputs!$C$78-Inputs!$C$79</f>
@@ -5628,7 +5643,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B26" s="37" t="n">
         <f aca="false">B24-B16-B25</f>
@@ -5637,7 +5652,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B27" s="24" t="n">
         <f aca="false">B26/B24</f>
@@ -5646,7 +5661,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">B16/Inputs!$C$12</f>
@@ -5655,7 +5670,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">B16/Inputs!$C$33</f>
@@ -5664,30 +5679,30 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B32" s="6" t="n">
         <f aca="false">History!D5</f>
@@ -5716,7 +5731,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C33" s="3" t="n">
         <f aca="false">Inputs!$F$88</f>
@@ -5741,7 +5756,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C34" s="27" t="n">
         <f aca="false">C32*C35</f>
@@ -5766,7 +5781,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C35" s="3" t="n">
         <f aca="false">Inputs!$F$89</f>
@@ -5791,7 +5806,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C36" s="6" t="n">
         <f aca="false">C32*Inputs!$C$101</f>
@@ -5816,7 +5831,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C37" s="6" t="n">
         <f aca="false">(C32-B32)*Inputs!$C$46</f>
@@ -5841,7 +5856,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C38" s="6" t="n">
         <f aca="false">C32*Inputs!$C$102</f>
@@ -5866,7 +5881,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C39" s="38" t="n">
         <f aca="false">Inputs!$C$84</f>
@@ -5891,7 +5906,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C40" s="22" t="n">
         <f aca="false">Inputs!$F$75</f>
@@ -5916,7 +5931,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C41" s="27" t="n">
         <f aca="false">$B$17</f>
@@ -5941,7 +5956,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C42" s="6" t="n">
         <f aca="false">C41*(C40+Inputs!$C$67)*C39</f>
@@ -5966,7 +5981,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C43" s="6" t="n">
         <f aca="false">C53*(C40+Inputs!$C$72)*C39</f>
@@ -5991,7 +6006,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C44" s="27" t="n">
         <f aca="false">C42+C43</f>
@@ -6016,7 +6031,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C45" s="6" t="n">
         <f aca="false">MIN(C44,Inputs!$C$45*C34*C39)</f>
@@ -6041,7 +6056,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C46" s="6" t="n">
         <f aca="false">MAX(0,(C34-C38)*C39-C45)*Inputs!$C$44</f>
@@ -6066,7 +6081,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C47" s="28" t="n">
         <f aca="false">(C34-C36+C37-Inputs!$C$81)*C39-C44-C46</f>
@@ -6091,7 +6106,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C48" s="6" t="n">
         <f aca="false">MIN(C41,$B$17*Inputs!$C$70*C39)</f>
@@ -6116,7 +6131,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C49" s="6" t="n">
         <f aca="false">Inputs!$C$79</f>
@@ -6141,7 +6156,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C50" s="27" t="n">
         <f aca="false">C49+C47-C48</f>
@@ -6166,7 +6181,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C51" s="6" t="n">
         <f aca="false">MIN(MAX(0,C50-Inputs!$C$79)*Inputs!$C$80,C41-C48)</f>
@@ -6191,7 +6206,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C52" s="27" t="n">
         <f aca="false">C41-C48-C51</f>
@@ -6216,7 +6231,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C53" s="27" t="n">
         <f aca="false">$B$18</f>
@@ -6241,7 +6256,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C54" s="27" t="n">
         <f aca="false">C50-C51</f>
@@ -6266,7 +6281,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C55" s="39" t="n">
         <f aca="false">C52+C53-C54</f>
@@ -6291,7 +6306,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C56" s="32" t="n">
         <f aca="false">(C52+C53)/C34</f>
@@ -6316,7 +6331,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C57" s="32" t="n">
         <f aca="false">C34*C39/C44</f>
@@ -6341,28 +6356,28 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6517,7 +6532,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B66" s="27" t="n">
         <f aca="false">MIN(C54:G54)</f>
@@ -6526,12 +6541,12 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="36" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B70" s="5" t="n">
         <f aca="false">'LBO grid'!$C$3</f>
@@ -6540,7 +6555,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B71" s="5" t="n">
         <f aca="false">B70*Inputs!$C$66/(Inputs!$C$66+Inputs!$C$71)</f>
@@ -6549,7 +6564,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B72" s="33" t="n">
         <f aca="false">B70-B71</f>
@@ -6558,7 +6573,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B73" s="5" t="n">
         <f aca="false">Inputs!$C$7*Inputs!$C$99</f>
@@ -6567,7 +6582,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B74" s="5" t="n">
         <f aca="false">B73-Inputs!$C$100</f>
@@ -6576,7 +6591,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B75" s="6" t="n">
         <f aca="false">B71*(1-Inputs!$C$68)+B72*(1-Inputs!$C$73)</f>
@@ -6585,7 +6600,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B76" s="6" t="n">
         <f aca="false">B70*Inputs!$C$76</f>
@@ -6594,7 +6609,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B77" s="6" t="n">
         <f aca="false">B74*Inputs!$C$77</f>
@@ -6603,7 +6618,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B78" s="37" t="n">
         <f aca="false">B73+B75+B76+B77</f>
@@ -6612,7 +6627,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B79" s="6" t="n">
         <f aca="false">Inputs!$C$78-Inputs!$C$79</f>
@@ -6621,7 +6636,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B80" s="37" t="n">
         <f aca="false">B78-B70-B79</f>
@@ -6630,7 +6645,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B81" s="24" t="n">
         <f aca="false">B80/B78</f>
@@ -6639,7 +6654,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B82" s="4" t="n">
         <f aca="false">B70/Inputs!$C$12</f>
@@ -6648,7 +6663,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B83" s="4" t="n">
         <f aca="false">B70/Inputs!$C$33</f>
@@ -6657,30 +6672,30 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B86" s="6" t="n">
         <f aca="false">History!D5</f>
@@ -6709,7 +6724,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C87" s="3" t="n">
         <f aca="false">Inputs!$F$88</f>
@@ -6734,7 +6749,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C88" s="27" t="n">
         <f aca="false">C86*C89</f>
@@ -6759,7 +6774,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C89" s="3" t="n">
         <f aca="false">Inputs!$F$89</f>
@@ -6784,7 +6799,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C90" s="6" t="n">
         <f aca="false">C86*Inputs!$C$101</f>
@@ -6809,7 +6824,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C91" s="6" t="n">
         <f aca="false">(C86-B86)*Inputs!$C$46</f>
@@ -6834,7 +6849,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C92" s="6" t="n">
         <f aca="false">C86*Inputs!$C$102</f>
@@ -6859,7 +6874,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C93" s="38" t="n">
         <f aca="false">Inputs!$C$84</f>
@@ -6884,7 +6899,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C94" s="22" t="n">
         <f aca="false">Inputs!$F$75</f>
@@ -6909,7 +6924,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C95" s="27" t="n">
         <f aca="false">$B$71</f>
@@ -6934,7 +6949,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C96" s="6" t="n">
         <f aca="false">C95*(C94+Inputs!$C$67)*C93</f>
@@ -6959,7 +6974,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C97" s="6" t="n">
         <f aca="false">C107*(C94+Inputs!$C$72)*C93</f>
@@ -6984,7 +6999,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C98" s="27" t="n">
         <f aca="false">C96+C97</f>
@@ -7009,7 +7024,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C99" s="6" t="n">
         <f aca="false">MIN(C98,Inputs!$C$45*C88*C93)</f>
@@ -7034,7 +7049,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C100" s="6" t="n">
         <f aca="false">MAX(0,(C88-C92)*C93-C99)*Inputs!$C$44</f>
@@ -7059,7 +7074,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C101" s="28" t="n">
         <f aca="false">(C88-C90+C91-Inputs!$C$81)*C93-C98-C100</f>
@@ -7084,7 +7099,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C102" s="6" t="n">
         <f aca="false">MIN(C95,$B$71*Inputs!$C$70*C93)</f>
@@ -7109,7 +7124,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C103" s="6" t="n">
         <f aca="false">Inputs!$C$79</f>
@@ -7134,7 +7149,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C104" s="27" t="n">
         <f aca="false">C103+C101-C102</f>
@@ -7159,7 +7174,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C105" s="6" t="n">
         <f aca="false">MIN(MAX(0,C104-Inputs!$C$79)*Inputs!$C$80,C95-C102)</f>
@@ -7184,7 +7199,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C106" s="27" t="n">
         <f aca="false">C95-C102-C105</f>
@@ -7209,7 +7224,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C107" s="27" t="n">
         <f aca="false">$B$72</f>
@@ -7234,7 +7249,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C108" s="27" t="n">
         <f aca="false">C104-C105</f>
@@ -7259,7 +7274,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C109" s="39" t="n">
         <f aca="false">C106+C107-C108</f>
@@ -7284,7 +7299,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C110" s="32" t="n">
         <f aca="false">(C106+C107)/C88</f>
@@ -7309,7 +7324,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C111" s="32" t="n">
         <f aca="false">C88*C93/C98</f>
@@ -7334,28 +7349,28 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7510,7 +7525,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B120" s="27" t="n">
         <f aca="false">MIN(C108:G108)</f>
@@ -7519,12 +7534,12 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="36" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B124" s="5" t="n">
         <f aca="false">'LBO grid'!$D$3</f>
@@ -7533,7 +7548,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B125" s="5" t="n">
         <f aca="false">B124*Inputs!$C$66/(Inputs!$C$66+Inputs!$C$71)</f>
@@ -7542,7 +7557,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B126" s="33" t="n">
         <f aca="false">B124-B125</f>
@@ -7551,7 +7566,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B127" s="5" t="n">
         <f aca="false">Inputs!$C$7*Inputs!$C$99</f>
@@ -7560,7 +7575,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B128" s="5" t="n">
         <f aca="false">B127-Inputs!$C$100</f>
@@ -7569,7 +7584,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B129" s="6" t="n">
         <f aca="false">B125*(1-Inputs!$C$68)+B126*(1-Inputs!$C$73)</f>
@@ -7578,7 +7593,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B130" s="6" t="n">
         <f aca="false">B124*Inputs!$C$76</f>
@@ -7587,7 +7602,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B131" s="6" t="n">
         <f aca="false">B128*Inputs!$C$77</f>
@@ -7596,7 +7611,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B132" s="37" t="n">
         <f aca="false">B127+B129+B130+B131</f>
@@ -7605,7 +7620,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B133" s="6" t="n">
         <f aca="false">Inputs!$C$78-Inputs!$C$79</f>
@@ -7614,7 +7629,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B134" s="37" t="n">
         <f aca="false">B132-B124-B133</f>
@@ -7623,7 +7638,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B135" s="24" t="n">
         <f aca="false">B134/B132</f>
@@ -7632,7 +7647,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B136" s="4" t="n">
         <f aca="false">B124/Inputs!$C$12</f>
@@ -7641,7 +7656,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B137" s="4" t="n">
         <f aca="false">B124/Inputs!$C$33</f>
@@ -7650,30 +7665,30 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B140" s="6" t="n">
         <f aca="false">History!D5</f>
@@ -7702,7 +7717,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C141" s="3" t="n">
         <f aca="false">Inputs!$F$88</f>
@@ -7727,7 +7742,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C142" s="27" t="n">
         <f aca="false">C140*C143</f>
@@ -7752,7 +7767,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C143" s="3" t="n">
         <f aca="false">Inputs!$F$89</f>
@@ -7777,7 +7792,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C144" s="6" t="n">
         <f aca="false">C140*Inputs!$C$101</f>
@@ -7802,7 +7817,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C145" s="6" t="n">
         <f aca="false">(C140-B140)*Inputs!$C$46</f>
@@ -7827,7 +7842,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C146" s="6" t="n">
         <f aca="false">C140*Inputs!$C$102</f>
@@ -7852,7 +7867,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C147" s="38" t="n">
         <f aca="false">Inputs!$C$84</f>
@@ -7877,7 +7892,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C148" s="22" t="n">
         <f aca="false">Inputs!$F$75</f>
@@ -7902,7 +7917,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C149" s="27" t="n">
         <f aca="false">$B$125</f>
@@ -7927,7 +7942,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C150" s="6" t="n">
         <f aca="false">C149*(C148+Inputs!$C$67)*C147</f>
@@ -7952,7 +7967,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C151" s="6" t="n">
         <f aca="false">C161*(C148+Inputs!$C$72)*C147</f>
@@ -7977,7 +7992,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C152" s="27" t="n">
         <f aca="false">C150+C151</f>
@@ -8002,7 +8017,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C153" s="6" t="n">
         <f aca="false">MIN(C152,Inputs!$C$45*C142*C147)</f>
@@ -8027,7 +8042,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C154" s="6" t="n">
         <f aca="false">MAX(0,(C142-C146)*C147-C153)*Inputs!$C$44</f>
@@ -8052,7 +8067,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C155" s="28" t="n">
         <f aca="false">(C142-C144+C145-Inputs!$C$81)*C147-C152-C154</f>
@@ -8077,7 +8092,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C156" s="6" t="n">
         <f aca="false">MIN(C149,$B$125*Inputs!$C$70*C147)</f>
@@ -8102,7 +8117,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C157" s="6" t="n">
         <f aca="false">Inputs!$C$79</f>
@@ -8127,7 +8142,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C158" s="27" t="n">
         <f aca="false">C157+C155-C156</f>
@@ -8152,7 +8167,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C159" s="6" t="n">
         <f aca="false">MIN(MAX(0,C158-Inputs!$C$79)*Inputs!$C$80,C149-C156)</f>
@@ -8177,7 +8192,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C160" s="27" t="n">
         <f aca="false">C149-C156-C159</f>
@@ -8202,7 +8217,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C161" s="27" t="n">
         <f aca="false">$B$126</f>
@@ -8227,7 +8242,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C162" s="27" t="n">
         <f aca="false">C158-C159</f>
@@ -8252,7 +8267,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C163" s="39" t="n">
         <f aca="false">C160+C161-C162</f>
@@ -8277,7 +8292,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C164" s="32" t="n">
         <f aca="false">(C160+C161)/C142</f>
@@ -8302,7 +8317,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C165" s="32" t="n">
         <f aca="false">C142*C147/C152</f>
@@ -8327,28 +8342,28 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H167" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8503,7 +8518,7 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B174" s="27" t="n">
         <f aca="false">MIN(C162:G162)</f>
@@ -8512,12 +8527,12 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="36" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B178" s="5" t="n">
         <f aca="false">'LBO grid'!$E$3</f>
@@ -8526,7 +8541,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B179" s="5" t="n">
         <f aca="false">B178*Inputs!$C$66/(Inputs!$C$66+Inputs!$C$71)</f>
@@ -8535,7 +8550,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B180" s="33" t="n">
         <f aca="false">B178-B179</f>
@@ -8544,7 +8559,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B181" s="5" t="n">
         <f aca="false">Inputs!$C$7*Inputs!$C$99</f>
@@ -8553,7 +8568,7 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B182" s="5" t="n">
         <f aca="false">B181-Inputs!$C$100</f>
@@ -8562,7 +8577,7 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B183" s="6" t="n">
         <f aca="false">B179*(1-Inputs!$C$68)+B180*(1-Inputs!$C$73)</f>
@@ -8571,7 +8586,7 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B184" s="6" t="n">
         <f aca="false">B178*Inputs!$C$76</f>
@@ -8580,7 +8595,7 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B185" s="6" t="n">
         <f aca="false">B182*Inputs!$C$77</f>
@@ -8589,7 +8604,7 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B186" s="37" t="n">
         <f aca="false">B181+B183+B184+B185</f>
@@ -8598,7 +8613,7 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B187" s="6" t="n">
         <f aca="false">Inputs!$C$78-Inputs!$C$79</f>
@@ -8607,7 +8622,7 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B188" s="37" t="n">
         <f aca="false">B186-B178-B187</f>
@@ -8616,7 +8631,7 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B189" s="24" t="n">
         <f aca="false">B188/B186</f>
@@ -8625,7 +8640,7 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B190" s="4" t="n">
         <f aca="false">B178/Inputs!$C$12</f>
@@ -8634,7 +8649,7 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B191" s="4" t="n">
         <f aca="false">B178/Inputs!$C$33</f>
@@ -8643,30 +8658,30 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B194" s="6" t="n">
         <f aca="false">History!D5</f>
@@ -8695,7 +8710,7 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C195" s="3" t="n">
         <f aca="false">Inputs!$F$88</f>
@@ -8720,7 +8735,7 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C196" s="27" t="n">
         <f aca="false">C194*C197</f>
@@ -8745,7 +8760,7 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C197" s="3" t="n">
         <f aca="false">Inputs!$F$89</f>
@@ -8770,7 +8785,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C198" s="6" t="n">
         <f aca="false">C194*Inputs!$C$101</f>
@@ -8795,7 +8810,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C199" s="6" t="n">
         <f aca="false">(C194-B194)*Inputs!$C$46</f>
@@ -8820,7 +8835,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C200" s="6" t="n">
         <f aca="false">C194*Inputs!$C$102</f>
@@ -8845,7 +8860,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C201" s="38" t="n">
         <f aca="false">Inputs!$C$84</f>
@@ -8870,7 +8885,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C202" s="22" t="n">
         <f aca="false">Inputs!$F$75</f>
@@ -8895,7 +8910,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C203" s="27" t="n">
         <f aca="false">$B$179</f>
@@ -8920,7 +8935,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C204" s="6" t="n">
         <f aca="false">C203*(C202+Inputs!$C$67)*C201</f>
@@ -8945,7 +8960,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C205" s="6" t="n">
         <f aca="false">C215*(C202+Inputs!$C$72)*C201</f>
@@ -8970,7 +8985,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C206" s="27" t="n">
         <f aca="false">C204+C205</f>
@@ -8995,7 +9010,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C207" s="6" t="n">
         <f aca="false">MIN(C206,Inputs!$C$45*C196*C201)</f>
@@ -9020,7 +9035,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C208" s="6" t="n">
         <f aca="false">MAX(0,(C196-C200)*C201-C207)*Inputs!$C$44</f>
@@ -9045,7 +9060,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C209" s="28" t="n">
         <f aca="false">(C196-C198+C199-Inputs!$C$81)*C201-C206-C208</f>
@@ -9070,7 +9085,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C210" s="6" t="n">
         <f aca="false">MIN(C203,$B$179*Inputs!$C$70*C201)</f>
@@ -9095,7 +9110,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C211" s="6" t="n">
         <f aca="false">Inputs!$C$79</f>
@@ -9120,7 +9135,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C212" s="27" t="n">
         <f aca="false">C211+C209-C210</f>
@@ -9145,7 +9160,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C213" s="6" t="n">
         <f aca="false">MIN(MAX(0,C212-Inputs!$C$79)*Inputs!$C$80,C203-C210)</f>
@@ -9170,7 +9185,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C214" s="27" t="n">
         <f aca="false">C203-C210-C213</f>
@@ -9195,7 +9210,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C215" s="27" t="n">
         <f aca="false">$B$180</f>
@@ -9220,7 +9235,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C216" s="27" t="n">
         <f aca="false">C212-C213</f>
@@ -9245,7 +9260,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C217" s="39" t="n">
         <f aca="false">C214+C215-C216</f>
@@ -9270,7 +9285,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C218" s="32" t="n">
         <f aca="false">(C214+C215)/C196</f>
@@ -9295,7 +9310,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C219" s="32" t="n">
         <f aca="false">C196*C201/C206</f>
@@ -9320,28 +9335,28 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G221" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H221" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9496,7 +9511,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B228" s="27" t="n">
         <f aca="false">MIN(C216:G216)</f>
@@ -9505,12 +9520,12 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="36" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B232" s="5" t="n">
         <f aca="false">'LBO grid'!$F$3</f>
@@ -9519,7 +9534,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B233" s="5" t="n">
         <f aca="false">B232*Inputs!$C$66/(Inputs!$C$66+Inputs!$C$71)</f>
@@ -9528,7 +9543,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B234" s="33" t="n">
         <f aca="false">B232-B233</f>
@@ -9537,7 +9552,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B235" s="5" t="n">
         <f aca="false">Inputs!$C$7*Inputs!$C$99</f>
@@ -9546,7 +9561,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B236" s="5" t="n">
         <f aca="false">B235-Inputs!$C$100</f>
@@ -9555,7 +9570,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B237" s="6" t="n">
         <f aca="false">B233*(1-Inputs!$C$68)+B234*(1-Inputs!$C$73)</f>
@@ -9564,7 +9579,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B238" s="6" t="n">
         <f aca="false">B232*Inputs!$C$76</f>
@@ -9573,7 +9588,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B239" s="6" t="n">
         <f aca="false">B236*Inputs!$C$77</f>
@@ -9582,7 +9597,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B240" s="37" t="n">
         <f aca="false">B235+B237+B238+B239</f>
@@ -9591,7 +9606,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B241" s="6" t="n">
         <f aca="false">Inputs!$C$78-Inputs!$C$79</f>
@@ -9600,7 +9615,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B242" s="37" t="n">
         <f aca="false">B240-B232-B241</f>
@@ -9609,7 +9624,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B243" s="24" t="n">
         <f aca="false">B242/B240</f>
@@ -9618,7 +9633,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B244" s="4" t="n">
         <f aca="false">B232/Inputs!$C$12</f>
@@ -9627,7 +9642,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B245" s="4" t="n">
         <f aca="false">B232/Inputs!$C$33</f>
@@ -9636,30 +9651,30 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D247" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G247" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B248" s="6" t="n">
         <f aca="false">History!D5</f>
@@ -9688,7 +9703,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C249" s="3" t="n">
         <f aca="false">Inputs!$F$88</f>
@@ -9713,7 +9728,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C250" s="27" t="n">
         <f aca="false">C248*C251</f>
@@ -9738,7 +9753,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C251" s="3" t="n">
         <f aca="false">Inputs!$F$89</f>
@@ -9763,7 +9778,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C252" s="6" t="n">
         <f aca="false">C248*Inputs!$C$101</f>
@@ -9788,7 +9803,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C253" s="6" t="n">
         <f aca="false">(C248-B248)*Inputs!$C$46</f>
@@ -9813,7 +9828,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C254" s="6" t="n">
         <f aca="false">C248*Inputs!$C$102</f>
@@ -9838,7 +9853,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C255" s="38" t="n">
         <f aca="false">Inputs!$C$84</f>
@@ -9863,7 +9878,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C256" s="22" t="n">
         <f aca="false">Inputs!$F$75</f>
@@ -9888,7 +9903,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C257" s="27" t="n">
         <f aca="false">$B$233</f>
@@ -9913,7 +9928,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C258" s="6" t="n">
         <f aca="false">C257*(C256+Inputs!$C$67)*C255</f>
@@ -9938,7 +9953,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C259" s="6" t="n">
         <f aca="false">C269*(C256+Inputs!$C$72)*C255</f>
@@ -9963,7 +9978,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C260" s="27" t="n">
         <f aca="false">C258+C259</f>
@@ -9988,7 +10003,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C261" s="6" t="n">
         <f aca="false">MIN(C260,Inputs!$C$45*C250*C255)</f>
@@ -10013,7 +10028,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C262" s="6" t="n">
         <f aca="false">MAX(0,(C250-C254)*C255-C261)*Inputs!$C$44</f>
@@ -10038,7 +10053,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C263" s="28" t="n">
         <f aca="false">(C250-C252+C253-Inputs!$C$81)*C255-C260-C262</f>
@@ -10063,7 +10078,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C264" s="6" t="n">
         <f aca="false">MIN(C257,$B$233*Inputs!$C$70*C255)</f>
@@ -10088,7 +10103,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C265" s="6" t="n">
         <f aca="false">Inputs!$C$79</f>
@@ -10113,7 +10128,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C266" s="27" t="n">
         <f aca="false">C265+C263-C264</f>
@@ -10138,7 +10153,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C267" s="6" t="n">
         <f aca="false">MIN(MAX(0,C266-Inputs!$C$79)*Inputs!$C$80,C257-C264)</f>
@@ -10163,7 +10178,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C268" s="27" t="n">
         <f aca="false">C257-C264-C267</f>
@@ -10188,7 +10203,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C269" s="27" t="n">
         <f aca="false">$B$234</f>
@@ -10213,7 +10228,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C270" s="27" t="n">
         <f aca="false">C266-C267</f>
@@ -10238,7 +10253,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C271" s="39" t="n">
         <f aca="false">C268+C269-C270</f>
@@ -10263,7 +10278,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C272" s="32" t="n">
         <f aca="false">(C268+C269)/C250</f>
@@ -10288,7 +10303,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C273" s="32" t="n">
         <f aca="false">C250*C255/C260</f>
@@ -10313,28 +10328,28 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D275" s="7" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E275" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F275" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G275" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H275" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10489,7 +10504,7 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B282" s="27" t="n">
         <f aca="false">MIN(C270:G270)</f>
@@ -10520,17 +10535,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">LBO!$F$49</f>
@@ -10539,7 +10554,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>0.2</v>
@@ -10547,7 +10562,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">B4/(1+B6)^Inputs!$C$85</f>
@@ -10556,7 +10571,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B8" s="26" t="n">
         <f aca="false">(B7+LBO!$K$3+LBO!$B$14-LBO!$B$10-LBO!$B$11+Inputs!$C$77*Inputs!$C$100)/(Inputs!$C$99*(1+Inputs!$C$77))</f>
@@ -10565,7 +10580,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B9" s="31" t="n">
         <f aca="false">B8*100/Inputs!$C$98</f>
@@ -10574,7 +10589,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>0.25</v>
@@ -10582,7 +10597,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">B4/(1+B10)^Inputs!$C$85</f>
@@ -10591,7 +10606,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">(B11+LBO!$K$3+LBO!$B$14-LBO!$B$10-LBO!$B$11+Inputs!$C$77*Inputs!$C$100)/(Inputs!$C$99*(1+Inputs!$C$77))</f>
@@ -10600,7 +10615,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B13" s="31" t="n">
         <f aca="false">B12*100/Inputs!$C$98</f>
@@ -10609,7 +10624,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">Inputs!$C$63</f>
@@ -10618,7 +10633,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B15" s="5" t="n">
         <f aca="false">B4/(1+B14)^Inputs!$C$85</f>
@@ -10627,7 +10642,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B16" s="26" t="n">
         <f aca="false">(B15+LBO!$K$3+LBO!$B$14-LBO!$B$10-LBO!$B$11+Inputs!$C$77*Inputs!$C$100)/(Inputs!$C$99*(1+Inputs!$C$77))</f>
@@ -10636,7 +10651,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B17" s="31" t="n">
         <f aca="false">B16*100/Inputs!$C$98</f>
@@ -10654,7 +10669,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">LBO!$H$49</f>
@@ -10686,430 +10701,430 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -11138,55 +11153,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -11202,347 +11217,347 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>7.75</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>620</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>5315</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>4992</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>616</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="0" t="s">
         <v>47</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>44</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>146</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>8.1</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>34.2</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>517</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>429.9</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>518.6</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>425</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>250</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>0.2</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C21" s="15" t="n">
         <v>0.443</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>0.1471</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C23" s="16" t="n">
         <v>0.9955</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C24" s="16" t="n">
         <v>0.6529</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C25" s="17" t="n">
         <v>383.2</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C26" s="17" t="n">
         <v>60.2</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -11558,313 +11573,313 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C29" s="17" t="n">
         <v>415.5</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C30" s="17" t="n">
         <v>545.4</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C31" s="17" t="n">
         <v>689.5</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C32" s="17" t="n">
         <v>637.3</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C33" s="17" t="n">
         <v>782.2</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C34" s="15" t="n">
         <v>1.066</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C35" s="15" t="n">
         <v>0.063</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C36" s="17" t="n">
         <v>330.3</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C37" s="17" t="n">
         <v>259.3</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C38" s="17" t="n">
         <v>84.5</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C39" s="17" t="n">
         <v>45.2</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C40" s="17" t="n">
         <v>71</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C41" s="17" t="n">
         <v>22.7</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C42" s="17" t="n">
         <v>8</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C43" s="15" t="n">
         <v>0.23</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C44" s="15" t="n">
         <v>0.25</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C45" s="15" t="n">
         <v>0.3</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C46" s="15" t="n">
         <v>0.1</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -11880,16 +11895,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F49" s="15" t="n">
         <v>0.21</v>
@@ -11915,16 +11930,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F50" s="15" t="n">
         <v>0.24</v>
@@ -11950,16 +11965,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F51" s="15" t="n">
         <v>0.065</v>
@@ -11985,86 +12000,86 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C52" s="16" t="n">
         <v>0.0454</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C53" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C54" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C55" s="15" t="n">
         <v>0.035</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C56" s="19" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -12080,80 +12095,80 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C59" s="15" t="n">
         <v>0.1</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>10</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C61" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C62" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C63" s="15" t="n">
         <v>0.2</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
@@ -12169,169 +12184,169 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C66" s="12" t="n">
         <v>1735</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C67" s="16" t="n">
         <v>0.0325</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C68" s="20" t="n">
         <v>0.995</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C69" s="19" t="n">
         <v>7</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C70" s="15" t="n">
         <v>0.01</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C71" s="12" t="n">
         <v>410</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C72" s="16" t="n">
         <v>0.0525</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C73" s="20" t="n">
         <v>0.995</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C74" s="19" t="n">
         <v>8</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F75" s="16" t="n">
         <v>0.046</v>
@@ -12351,159 +12366,159 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C76" s="15" t="n">
         <v>0.025</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C77" s="15" t="n">
         <v>0.01</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C78" s="17" t="n">
         <v>383.2</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C79" s="12" t="n">
         <v>100</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C80" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C81" s="12" t="n">
         <v>20</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C82" s="15" t="n">
         <v>0.08</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C83" s="17" t="n">
         <v>60.2</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C84" s="18" t="n">
         <v>0.75</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C85" s="18" t="n">
         <v>4.75</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
@@ -12519,13 +12534,13 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F88" s="15" t="n">
         <v>0.19</v>
@@ -12545,16 +12560,16 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F89" s="15" t="n">
         <v>0.27</v>
@@ -12574,21 +12589,21 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C90" s="13" t="n">
         <v>18</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
@@ -12604,13 +12619,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F93" s="15" t="n">
         <v>0.12</v>
@@ -12630,16 +12645,16 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F94" s="15" t="n">
         <v>0.24</v>
@@ -12659,21 +12674,21 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C95" s="13" t="n">
         <v>14</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
@@ -12689,112 +12704,112 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C98" s="21" t="n">
         <f aca="false">Inputs!$C$7/(Inputs!$C$8/100)</f>
         <v>1.25</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C99" s="6" t="n">
         <f aca="false">Inputs!$C$9/Inputs!$C$7</f>
         <v>685.806451612903</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C100" s="6" t="n">
         <f aca="false">Inputs!$C$9-Inputs!$C$10</f>
         <v>323</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C101" s="3" t="n">
         <f aca="false">Inputs!$C$42/Inputs!$C$36</f>
         <v>0.0242204056917953</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C102" s="3" t="n">
         <f aca="false">(Inputs!$C$38-Inputs!$C$40)/Inputs!$C$36</f>
         <v>0.0408719346049046</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C103" s="22" t="n">
         <f aca="false">Inputs!$C$52+Inputs!$C$53*Inputs!$C$54</f>
         <v>0.1079</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C104" s="23" t="n">
         <v>0.166666666666667</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -12821,26 +12836,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">Inputs!$C$29</f>
@@ -12857,7 +12872,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C6" s="24" t="n">
         <f aca="false">C5/B5-1</f>
@@ -12870,7 +12885,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">Inputs!$C$32</f>
@@ -12883,7 +12898,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D8" s="24" t="n">
         <f aca="false">D7/C7-1</f>
@@ -12892,7 +12907,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">Inputs!$C$12-Inputs!$C$38+Inputs!$C$39</f>
@@ -12905,7 +12920,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C10" s="24" t="n">
         <f aca="false">C9/C5</f>
@@ -12918,12 +12933,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B13" s="6" t="n">
         <f aca="false">Inputs!$C$30+Inputs!$C$36-Inputs!$C$37</f>
@@ -12932,7 +12947,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B14" s="6" t="n">
         <f aca="false">Inputs!$C$11</f>
@@ -12941,7 +12956,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">Inputs!$C$41/Inputs!$C$36</f>
@@ -12950,7 +12965,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">Inputs!$C$38/Inputs!$C$36</f>
@@ -12959,7 +12974,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B17" s="3" t="n">
         <f aca="false">Inputs!$C$34</f>
@@ -12995,17 +13010,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B4" s="26" t="n">
         <f aca="false">Inputs!$C$7</f>
@@ -13023,7 +13038,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B6" s="21" t="n">
         <f aca="false">Inputs!$C$98</f>
@@ -13032,7 +13047,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">Inputs!$C$99</f>
@@ -13041,7 +13056,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">Inputs!$C$9</f>
@@ -13050,7 +13065,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">Inputs!$C$100</f>
@@ -13059,7 +13074,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">Inputs!$C$10</f>
@@ -13068,7 +13083,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B11" s="4" t="n">
         <f aca="false">Inputs!$C$10/Inputs!$C$11</f>
@@ -13077,7 +13092,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B12" s="4" t="n">
         <f aca="false">Inputs!$C$13</f>
@@ -13086,7 +13101,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B13" s="4" t="n">
         <f aca="false">Inputs!$C$10/Inputs!$C$12</f>
@@ -13095,7 +13110,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B14" s="4" t="n">
         <f aca="false">Inputs!$C$14</f>
@@ -13104,7 +13119,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B15" s="4" t="n">
         <f aca="false">Inputs!$C$10/Inputs!$C$33</f>
@@ -13113,7 +13128,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">Inputs!$C$8/Inputs!$C$15-1</f>
@@ -13122,7 +13137,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B17" s="3" t="n">
         <f aca="false">Inputs!$C$20</f>
@@ -13131,7 +13146,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">Inputs!$C$8/Inputs!$C$16-1</f>
@@ -13140,7 +13155,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">Inputs!$C$21</f>
@@ -13149,7 +13164,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">Inputs!$C$8/Inputs!$C$17-1</f>
@@ -13158,7 +13173,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B21" s="3" t="n">
         <f aca="false">Inputs!$C$8/Inputs!$C$18-1</f>
@@ -13167,7 +13182,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B22" s="4" t="n">
         <f aca="false">Inputs!$C$8/Inputs!$C$19</f>
@@ -13176,7 +13191,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B23" s="3" t="n">
         <f aca="false">Inputs!$C$15/Inputs!$C$16-1</f>
@@ -13185,7 +13200,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B24" s="3" t="n">
         <f aca="false">Inputs!$C$22</f>
@@ -13194,7 +13209,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B25" s="22" t="n">
         <f aca="false">Inputs!$C$23</f>
@@ -13203,7 +13218,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B26" s="22" t="n">
         <f aca="false">Inputs!$C$24</f>
@@ -13212,79 +13227,79 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -13311,46 +13326,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">History!D5</f>
@@ -13387,7 +13402,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">Inputs!$F$49</f>
@@ -13420,7 +13435,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5*C8</f>
@@ -13453,7 +13468,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C8" s="3" t="n">
         <f aca="false">Inputs!$F$50</f>
@@ -13486,7 +13501,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">C5*Inputs!$F$51</f>
@@ -13519,7 +13534,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">C5*Inputs!$C$102</f>
@@ -13552,7 +13567,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C11" s="27" t="n">
         <f aca="false">C7-C9-C10</f>
@@ -13585,7 +13600,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C12" s="6" t="n">
         <f aca="false">MAX(0,C11)*Inputs!$C$44</f>
@@ -13618,7 +13633,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">C5*Inputs!$C$101</f>
@@ -13651,7 +13666,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C14" s="6" t="n">
         <f aca="false">(C5-B5)*Inputs!$C$46</f>
@@ -13684,7 +13699,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C15" s="28" t="n">
         <f aca="false">C7-C9*Inputs!$C$56-C12-C13+C14</f>
@@ -13717,7 +13732,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C16" s="29" t="n">
         <f aca="false">0+0.5</f>
@@ -13750,7 +13765,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C17" s="30" t="n">
         <f aca="false">1/(1+Inputs!$C$103)^C16</f>
@@ -13783,7 +13798,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C18" s="27" t="n">
         <f aca="false">C15*C17</f>
@@ -13816,7 +13831,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">Inputs!$C$103</f>
@@ -13825,7 +13840,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B22" s="3" t="n">
         <f aca="false">Inputs!$C$55</f>
@@ -13834,7 +13849,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B23" s="27" t="n">
         <f aca="false">SUM(C18:I18)</f>
@@ -13843,7 +13858,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B24" s="27" t="n">
         <f aca="false">I15*(1+B22)/(B21-B22)</f>
@@ -13852,7 +13867,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B25" s="27" t="n">
         <f aca="false">B24/(1+B21)^7</f>
@@ -13861,7 +13876,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B26" s="27" t="n">
         <f aca="false">B23+B25</f>
@@ -13870,7 +13885,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B27" s="6" t="n">
         <f aca="false">Inputs!$C$100</f>
@@ -13879,7 +13894,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B28" s="27" t="n">
         <f aca="false">B26+B27</f>
@@ -13888,7 +13903,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">B28/Inputs!$C$99</f>
@@ -13897,7 +13912,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B30" s="31" t="n">
         <f aca="false">B29*100/Inputs!$C$98</f>
@@ -13906,7 +13921,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B31" s="3" t="n">
         <f aca="false">B30/Inputs!$C$8-1</f>
@@ -13915,7 +13930,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B32" s="3" t="n">
         <f aca="false">B30/Inputs!$C$15-1</f>
@@ -13924,7 +13939,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B33" s="24" t="n">
         <f aca="false">B25/B26</f>
@@ -13933,7 +13948,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B34" s="32" t="n">
         <f aca="false">B24/I7</f>
@@ -13942,7 +13957,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B35" s="4" t="n">
         <f aca="false">Inputs!$C$10/C7</f>
@@ -13951,7 +13966,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14132,64 +14147,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>282.64</v>
@@ -14210,7 +14225,7 @@
         <v>3055.6</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J5" s="33" t="n">
         <f aca="false">C5*D5</f>
@@ -14229,15 +14244,15 @@
         <v>0.294982982065716</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>277.71</v>
@@ -14258,7 +14273,7 @@
         <v>6892.7</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J6" s="33" t="n">
         <f aca="false">C6*D6</f>
@@ -14277,15 +14292,15 @@
         <v>0.157021196338155</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>63.4</v>
@@ -14306,7 +14321,7 @@
         <v>5304.8</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J7" s="33" t="n">
         <f aca="false">C7*D7</f>
@@ -14325,15 +14340,15 @@
         <v>0.0867516211732771</v>
       </c>
       <c r="N7" s="0" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>169.21</v>
@@ -14354,7 +14369,7 @@
         <v>1617</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J8" s="33" t="n">
         <f aca="false">C8*D8</f>
@@ -14373,15 +14388,15 @@
         <v>0.311069882498454</v>
       </c>
       <c r="N8" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>20.05</v>
@@ -14402,7 +14417,7 @@
         <v>621.2</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J9" s="33" t="n">
         <f aca="false">C9*D9</f>
@@ -14421,15 +14436,15 @@
         <v>0.311976819059884</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>44.31</v>
@@ -14450,7 +14465,7 @@
         <v>777.7</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J10" s="33" t="n">
         <f aca="false">C10*D10</f>
@@ -14469,15 +14484,15 @@
         <v>0.0955381252410954</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>44.83</v>
@@ -14498,7 +14513,7 @@
         <v>798.7</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J11" s="33" t="n">
         <f aca="false">C11*D11</f>
@@ -14517,12 +14532,12 @@
         <v>0.126831100538375</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K13" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L13" s="32" t="n">
         <f aca="false">PERCENTILE($L$5:$L$11,0.25)</f>
@@ -14531,7 +14546,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K14" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L14" s="32" t="n">
         <f aca="false">MEDIAN($L$5:$L$11)</f>
@@ -14540,7 +14555,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K15" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L15" s="32" t="n">
         <f aca="false">PERCENTILE($L$5:$L$11,0.75)</f>
@@ -14549,7 +14564,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K16" s="0" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L16" s="34" t="n">
         <f aca="false">SLOPE($L$5:$L$11,$M$5:$M$11)</f>
@@ -14558,7 +14573,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K17" s="0" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L17" s="34" t="n">
         <f aca="false">INTERCEPT($L$5:$L$11,$M$5:$M$11)</f>
@@ -14567,7 +14582,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K18" s="0" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L18" s="34" t="n">
         <f aca="false">RSQ($L$5:$L$11,$M$5:$M$11)</f>
@@ -14576,12 +14591,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">DCF!C5</f>
@@ -14590,7 +14605,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B23" s="6" t="n">
         <f aca="false">Inputs!$C$104*Inputs!$C$31+(1-Inputs!$C$104)*B22</f>
@@ -14599,7 +14614,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B24" s="3" t="n">
         <f aca="false">DCF!C6</f>
@@ -14617,7 +14632,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B26" s="4" t="n">
         <f aca="false">Comps!$L$17+Comps!$L$16*B24</f>
@@ -14626,7 +14641,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B27" s="2" t="n">
         <f aca="false">((Comps!$L$13*B23)+Inputs!$C$100)/Inputs!$C$99*100/Inputs!$C$98</f>
@@ -14635,7 +14650,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B28" s="2" t="n">
         <f aca="false">((Comps!$L$14*B23)+Inputs!$C$100)/Inputs!$C$99*100/Inputs!$C$98</f>
@@ -14644,7 +14659,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B29" s="2" t="n">
         <f aca="false">((Comps!$L$15*B23)+Inputs!$C$100)/Inputs!$C$99*100/Inputs!$C$98</f>
@@ -14653,7 +14668,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B30" s="2" t="n">
         <f aca="false">(((B26-1)*B23)+Inputs!$C$100)/Inputs!$C$99*100/Inputs!$C$98</f>
@@ -14662,7 +14677,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B31" s="2" t="n">
         <f aca="false">(((B26+1)*B23)+Inputs!$C$100)/Inputs!$C$99*100/Inputs!$C$98</f>
@@ -14695,55 +14710,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>268</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>3948</v>
@@ -14759,24 +14774,24 @@
         <v>0.371</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>12300</v>
@@ -14792,24 +14807,24 @@
         <v>0.34</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>5800</v>
@@ -14825,24 +14840,24 @@
         <v>0.16</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>7051.2</v>
@@ -14858,24 +14873,24 @@
         <v>0.48</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>2800</v>
@@ -14891,24 +14906,24 @@
         <v>0.63</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>2300</v>
@@ -14924,24 +14939,24 @@
         <v>0.53</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>4600</v>
@@ -14957,18 +14972,18 @@
         <v>0.44</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">Inputs!$C$10</f>
@@ -14987,12 +15002,12 @@
         <v>0.199226305609284</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F14" s="32" t="n">
         <f aca="false">PERCENTILE($F$5:$F$11,0.25)</f>
@@ -15005,7 +15020,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F15" s="32" t="n">
         <f aca="false">PERCENTILE($F$5:$F$11,0.5)</f>
@@ -15018,7 +15033,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F16" s="32" t="n">
         <f aca="false">PERCENTILE($F$5:$F$11,0.75)</f>
@@ -15031,12 +15046,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B19" s="2" t="n">
         <f aca="false">(($F$14*Inputs!$C$11)+Inputs!$C$100)/Inputs!$C$99*100/Inputs!$C$98</f>
@@ -15045,7 +15060,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B20" s="2" t="n">
         <f aca="false">(($F$15*Inputs!$C$11)+Inputs!$C$100)/Inputs!$C$99*100/Inputs!$C$98</f>
@@ -15054,7 +15069,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B21" s="2" t="n">
         <f aca="false">(($F$16*Inputs!$C$11)+Inputs!$C$100)/Inputs!$C$99*100/Inputs!$C$98</f>
@@ -15063,7 +15078,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B22" s="2" t="n">
         <f aca="false">Inputs!$C$15*(1+$G$14)</f>
@@ -15072,7 +15087,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B23" s="2" t="n">
         <f aca="false">Inputs!$C$15*(1+$G$15)</f>
@@ -15081,7 +15096,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B24" s="2" t="n">
         <f aca="false">Inputs!$C$15*(1+$G$16)</f>
@@ -15090,7 +15105,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B25" s="2" t="n">
         <f aca="false">Inputs!$C$16*(1+$G$15)</f>
@@ -15121,34 +15136,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B5" s="2" t="n">
         <f aca="false">Inputs!$C$18</f>
@@ -15169,7 +15184,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B6" s="2" t="n">
         <f aca="false">DCF!$C$44</f>
@@ -15190,7 +15205,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B7" s="2" t="n">
         <f aca="false">Comps!$B$27</f>
@@ -15211,7 +15226,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B8" s="2" t="n">
         <f aca="false">Comps!$B$30</f>
@@ -15232,7 +15247,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B9" s="2" t="n">
         <f aca="false">Precedents!$B$19</f>
@@ -15253,7 +15268,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B10" s="2" t="n">
         <f aca="false">Precedents!$B$22</f>
@@ -15274,7 +15289,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B11" s="2" t="n">
         <f aca="false">'Ability to pay'!$B$13</f>
@@ -15318,12 +15333,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B4" s="6" t="n">
         <f aca="false">DCF!C5</f>
@@ -15332,7 +15347,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">B4*Inputs!$C$59</f>
@@ -15341,7 +15356,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B6" s="6" t="n">
         <f aca="false">B5*(1-Inputs!$C$44)*Inputs!$C$60-B5*Inputs!$C$61</f>
@@ -15350,7 +15365,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">DCF!B26</f>
@@ -15359,7 +15374,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">B7+B6*Inputs!$C$62</f>
@@ -15368,7 +15383,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B9" s="2" t="n">
         <f aca="false">((B8)+Inputs!$C$100)/Inputs!$C$99*100/Inputs!$C$98</f>
@@ -15377,7 +15392,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B10" s="2" t="n">
         <f aca="false">'Ability to pay'!$B$17</f>
@@ -15386,7 +15401,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B11" s="2" t="n">
         <f aca="false">Inputs!$C$8</f>
@@ -15395,7 +15410,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">B9/B11-1</f>
@@ -15404,7 +15419,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B13" s="24" t="n">
         <f aca="false">B10/B11-1</f>
@@ -15413,7 +15428,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">1-Inputs!$C$22</f>
@@ -15422,7 +15437,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
